--- a/stigmergy_predictions.xlsx
+++ b/stigmergy_predictions.xlsx
@@ -2179,7 +2179,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B219" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B275" t="n">
         <v>1</v>
@@ -6603,7 +6603,7 @@
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B772" t="n">
         <v>0</v>
@@ -7611,7 +7611,7 @@
     </row>
     <row r="898">
       <c r="A898" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B898" t="n">
         <v>1</v>
@@ -8859,7 +8859,7 @@
     </row>
     <row r="1054">
       <c r="A1054" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1054" t="n">
         <v>0</v>
@@ -13523,7 +13523,7 @@
     </row>
     <row r="1637">
       <c r="A1637" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1637" t="n">
         <v>1</v>
@@ -14979,7 +14979,7 @@
     </row>
     <row r="1819">
       <c r="A1819" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1819" t="n">
         <v>0</v>
@@ -19587,7 +19587,7 @@
     </row>
     <row r="2395">
       <c r="A2395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2395" t="n">
         <v>0</v>
@@ -21123,7 +21123,7 @@
     </row>
     <row r="2587">
       <c r="A2587" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2587" t="n">
         <v>0</v>
@@ -23107,7 +23107,7 @@
     </row>
     <row r="2835">
       <c r="A2835" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2835" t="n">
         <v>1</v>
@@ -23131,7 +23131,7 @@
     </row>
     <row r="2838">
       <c r="A2838" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2838" t="n">
         <v>1</v>
@@ -23459,7 +23459,7 @@
     </row>
     <row r="2879">
       <c r="A2879" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2879" t="n">
         <v>1</v>
@@ -24507,7 +24507,7 @@
     </row>
     <row r="3010">
       <c r="A3010" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3010" t="n">
         <v>1</v>
@@ -27219,7 +27219,7 @@
     </row>
     <row r="3349">
       <c r="A3349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3349" t="n">
         <v>0</v>
@@ -34451,7 +34451,7 @@
     </row>
     <row r="4253">
       <c r="A4253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4253" t="n">
         <v>0</v>
@@ -34651,7 +34651,7 @@
     </row>
     <row r="4278">
       <c r="A4278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4278" t="n">
         <v>0</v>
@@ -37843,7 +37843,7 @@
     </row>
     <row r="4677">
       <c r="A4677" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4677" t="n">
         <v>0</v>
@@ -40459,7 +40459,7 @@
     </row>
     <row r="5004">
       <c r="A5004" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5004" t="n">
         <v>0</v>
@@ -41867,7 +41867,7 @@
     </row>
     <row r="5180">
       <c r="A5180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5180" t="n">
         <v>1</v>
@@ -41947,7 +41947,7 @@
     </row>
     <row r="5190">
       <c r="A5190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5190" t="n">
         <v>1</v>
@@ -45779,7 +45779,7 @@
     </row>
     <row r="5669">
       <c r="A5669" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5669" t="n">
         <v>1</v>
@@ -46523,7 +46523,7 @@
     </row>
     <row r="5762">
       <c r="A5762" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5762" t="n">
         <v>0</v>
@@ -48299,7 +48299,7 @@
     </row>
     <row r="5984">
       <c r="A5984" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5984" t="n">
         <v>1</v>
@@ -49307,7 +49307,7 @@
     </row>
     <row r="6110">
       <c r="A6110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6110" t="n">
         <v>0</v>
@@ -51627,7 +51627,7 @@
     </row>
     <row r="6400">
       <c r="A6400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6400" t="n">
         <v>0</v>
@@ -51835,7 +51835,7 @@
     </row>
     <row r="6426">
       <c r="A6426" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6426" t="n">
         <v>0</v>
@@ -54611,7 +54611,7 @@
     </row>
     <row r="6773">
       <c r="A6773" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6773" t="n">
         <v>1</v>
@@ -56939,7 +56939,7 @@
     </row>
     <row r="7064">
       <c r="A7064" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7064" t="n">
         <v>0</v>
@@ -66483,7 +66483,7 @@
     </row>
     <row r="8257">
       <c r="A8257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8257" t="n">
         <v>1</v>
@@ -71797,7 +71797,7 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B518" t="n">
         <v>0</v>
@@ -76061,7 +76061,7 @@
     </row>
     <row r="1051">
       <c r="A1051" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1051" t="n">
         <v>1</v>
@@ -81157,7 +81157,7 @@
     </row>
     <row r="1688">
       <c r="A1688" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1688" t="n">
         <v>0</v>
@@ -81469,7 +81469,7 @@
     </row>
     <row r="1727">
       <c r="A1727" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1727" t="n">
         <v>0</v>
@@ -86861,7 +86861,7 @@
     </row>
     <row r="2401">
       <c r="A2401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2401" t="n">
         <v>0</v>
@@ -89349,7 +89349,7 @@
     </row>
     <row r="2712">
       <c r="A2712" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2712" t="n">
         <v>0</v>
@@ -93837,7 +93837,7 @@
     </row>
     <row r="3273">
       <c r="A3273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3273" t="n">
         <v>0</v>
